--- a/詳細設計/画面詳細設計/01_SCR-001_ログイン画面詳細設計書_React.xlsx
+++ b/詳細設計/画面詳細設計/01_SCR-001_ログイン画面詳細設計書_React.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re6d9e01b2c934e02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R3087d55b448946fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_画面概要" sheetId="3" r:id="Re708a2a4f89a478c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_画面レイアウト" sheetId="4" r:id="R0c8a302732ac4cc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_画面項目" sheetId="5" r:id="R5cc5e9a95e8945e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Component_State" sheetId="6" r:id="R6bbe7917b4ea4f64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Event処理" sheetId="7" r:id="R2025cb14eff14535"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_API_Mapping" sheetId="8" r:id="R58c65fc6ebe34fce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Message_例外" sheetId="9" r:id="Red2e9c985aac4efc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_単体テスト観点" sheetId="10" r:id="Rb8a3f2c0670546a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rb3ff751f98324b88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Ra713412ff8264d5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_画面概要" sheetId="3" r:id="R5ae780e457f4443e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_画面レイアウト" sheetId="4" r:id="R171af198e2154e3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_画面項目" sheetId="5" r:id="R37cd7aaf898545ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Component_State" sheetId="6" r:id="R354d20bef5d649b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Event処理" sheetId="7" r:id="Rd2374e67b1e54c0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_API_Mapping" sheetId="8" r:id="R2f36e49c669344f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Message_例外" sheetId="9" r:id="R486eb63b9c1747a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_単体テスト観点" sheetId="10" r:id="R18ef82a3d2114434"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -877,7 +877,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="705">
+  <x:cellXfs count="706">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2924,6 +2924,9 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="27" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -3186,7 +3189,7 @@
       <x:c r="H2" s="2"/>
       <x:c r="I2" s="2"/>
       <x:c r="J2" s="2" t="str">
-        <x:v>Ver.2.3</x:v>
+        <x:v>Ver.2.4</x:v>
       </x:c>
       <x:c r="K2" s="2"/>
       <x:c r="L2" s="2"/>
@@ -3376,12 +3379,20 @@
       <x:c r="D15" s="36"/>
       <x:c r="E15" s="36"/>
       <x:c r="F15" s="38" t="str">
-        <x:v>Ver.2.3</x:v>
-      </x:c>
-      <x:c r="G15" s="38"/>
-      <x:c r="H15" s="38"/>
-      <x:c r="I15" s="38"/>
-      <x:c r="J15" s="38"/>
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="G15" s="38" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="H15" s="38" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="I15" s="38" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="J15" s="38" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
       <x:c r="K15" s="2"/>
       <x:c r="L15" s="2"/>
     </x:row>
@@ -3483,69 +3494,117 @@
     </x:row>
     <x:row r="22" ht="44" customHeight="1">
       <x:c r="A22" s="58" t="str">
-        <x:v>本書はSCR-001の実装基準。参照Baseline：BL-2026-09-24（基本設計Ver.2.5）。詳細設計Ver.2.3。基本設計の契約・業務Ruleを正とし、本書は画面固有処理を展開する。変更は変更管理に従う。</x:v>
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
       </x:c>
       <x:c r="B22" s="59" t="str">
-        <x:v>本書はSCR-001 ログイン画面の実装基準を定義する。参照元は認証・画面共通・権限・API・メッセージの各設計書とし、ITEM・VAL・STATE・EVT・API・MSG・UTを一貫したIDで管理する。</x:v>
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
       </x:c>
       <x:c r="C22" s="59" t="str">
-        <x:v>本書はSCR-001 ログイン画面の実装基準を定義する。参照元は認証・画面共通・権限・API・メッセージの各設計書とし、ITEM・VAL・STATE・EVT・API・MSG・UTを一貫したIDで管理する。</x:v>
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
       </x:c>
       <x:c r="D22" s="59" t="str">
-        <x:v>本書はSCR-001 ログイン画面の実装基準を定義する。参照元は認証・画面共通・権限・API・メッセージの各設計書とし、ITEM・VAL・STATE・EVT・API・MSG・UTを一貫したIDで管理する。</x:v>
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
       </x:c>
       <x:c r="E22" s="59" t="str">
-        <x:v>本書はSCR-001 ログイン画面の実装基準を定義する。参照元は認証・画面共通・権限・API・メッセージの各設計書とし、ITEM・VAL・STATE・EVT・API・MSG・UTを一貫したIDで管理する。</x:v>
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
       </x:c>
       <x:c r="F22" s="59" t="str">
-        <x:v>本書はSCR-001 ログイン画面の実装基準を定義する。参照元は認証・画面共通・権限・API・メッセージの各設計書とし、ITEM・VAL・STATE・EVT・API・MSG・UTを一貫したIDで管理する。</x:v>
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
       </x:c>
       <x:c r="G22" s="59" t="str">
-        <x:v>本書はSCR-001 ログイン画面の実装基準を定義する。参照元は認証・画面共通・権限・API・メッセージの各設計書とし、ITEM・VAL・STATE・EVT・API・MSG・UTを一貫したIDで管理する。</x:v>
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
       </x:c>
       <x:c r="H22" s="59" t="str">
-        <x:v>本書はSCR-001 ログイン画面の実装基準を定義する。参照元は認証・画面共通・権限・API・メッセージの各設計書とし、ITEM・VAL・STATE・EVT・API・MSG・UTを一貫したIDで管理する。</x:v>
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
       </x:c>
       <x:c r="I22" s="59" t="str">
-        <x:v>本書はSCR-001 ログイン画面の実装基準を定義する。参照元は認証・画面共通・権限・API・メッセージの各設計書とし、ITEM・VAL・STATE・EVT・API・MSG・UTを一貫したIDで管理する。</x:v>
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
       </x:c>
       <x:c r="J22" s="59" t="str">
-        <x:v>本書はSCR-001 ログイン画面の実装基準を定義する。参照元は認証・画面共通・権限・API・メッセージの各設計書とし、ITEM・VAL・STATE・EVT・API・MSG・UTを一貫したIDで管理する。</x:v>
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
       </x:c>
       <x:c r="K22" s="59" t="str">
-        <x:v>本書はSCR-001 ログイン画面の実装基準を定義する。参照元は認証・画面共通・権限・API・メッセージの各設計書とし、ITEM・VAL・STATE・EVT・API・MSG・UTを一貫したIDで管理する。</x:v>
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
       </x:c>
       <x:c r="L22" s="60" t="str">
-        <x:v>本書はSCR-001 ログイン画面の実装基準を定義する。参照元は認証・画面共通・権限・API・メッセージの各設計書とし、ITEM・VAL・STATE・EVT・API・MSG・UTを一貫したIDで管理する。</x:v>
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="61"/>
-      <x:c r="B23" s="62"/>
-      <x:c r="C23" s="62"/>
-      <x:c r="D23" s="62"/>
-      <x:c r="E23" s="62"/>
-      <x:c r="F23" s="62"/>
-      <x:c r="G23" s="62"/>
-      <x:c r="H23" s="62"/>
-      <x:c r="I23" s="62"/>
-      <x:c r="J23" s="62"/>
-      <x:c r="K23" s="62"/>
-      <x:c r="L23" s="63"/>
+      <x:c r="A23" s="61" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="B23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="C23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="D23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="E23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="F23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="G23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="H23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="I23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="J23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="K23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="L23" s="63" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="64"/>
-      <x:c r="B24" s="65"/>
-      <x:c r="C24" s="65"/>
-      <x:c r="D24" s="65"/>
-      <x:c r="E24" s="65"/>
-      <x:c r="F24" s="65"/>
-      <x:c r="G24" s="65"/>
-      <x:c r="H24" s="65"/>
-      <x:c r="I24" s="65"/>
-      <x:c r="J24" s="65"/>
-      <x:c r="K24" s="65"/>
-      <x:c r="L24" s="66"/>
+      <x:c r="A24" s="64" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="B24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="C24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="D24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="E24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="F24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="G24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="H24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="I24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="J24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="K24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="L24" s="66" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="2"/>
@@ -3704,10 +3763,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.3</x:v>
-      </x:c>
-      <x:c r="K2" s="80"/>
-      <x:c r="L2" s="80"/>
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="K2" s="80" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="L2" s="80" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="241"/>
@@ -4541,41 +4604,41 @@
         <x:v>07／08 No.12</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="56" customHeight="1">
-      <x:c r="A28" s="529" t="str">
+    <x:row r="28" ht="130" customHeight="1">
+      <x:c r="A28" s="705" t="str">
         <x:v>UT-019</x:v>
       </x:c>
-      <x:c r="B28" s="529" t="str">
+      <x:c r="B28" s="705" t="str">
         <x:v>CONTROL</x:v>
       </x:c>
-      <x:c r="C28" s="529" t="str">
+      <x:c r="C28" s="705" t="str">
         <x:v>EVT-002 Step1/4／STATE-003</x:v>
       </x:c>
-      <x:c r="D28" s="529" t="str">
-        <x:v>AUTH-001応答待ち</x:v>
-      </x:c>
-      <x:c r="E28" s="529" t="str">
+      <x:c r="D28" s="705" t="str">
+        <x:v>初期化完了、STATE-006=0、user01 / ValidPass1入力済。AUTH-001応答待ち。</x:v>
+      </x:c>
+      <x:c r="E28" s="705" t="str">
         <x:v>ITEM-003を連続2回Click</x:v>
       </x:c>
-      <x:c r="F28" s="529" t="str">
-        <x:v>1回目は応答待ち</x:v>
-      </x:c>
-      <x:c r="G28" s="529" t="str">
-        <x:v>Button非活性、2回目操作を受け付けない</x:v>
-      </x:c>
-      <x:c r="H28" s="529" t="str">
-        <x:v>STATE-003=true、AUTH-001は1回のみ</x:v>
-      </x:c>
-      <x:c r="I28" s="529" t="str">
+      <x:c r="F28" s="705" t="str">
+        <x:v>最初はPromise保留、その後401 / AUTH-4001で完了させる。AUTH-004未呼出。</x:v>
+      </x:c>
+      <x:c r="G28" s="705" t="str">
+        <x:v>待機中：ITEM-003 disabled、表示「ログイン中…」。完了後：表示「ログイン」、活性、MSG-E-019、ITEM-002 Focus。</x:v>
+      </x:c>
+      <x:c r="H28" s="705" t="str">
+        <x:v>STATE-003：true→false。AUTH-001は合計1回。username保持、passwordクリア。</x:v>
+      </x:c>
+      <x:c r="I28" s="705" t="str">
         <x:v>SCR-001</x:v>
       </x:c>
-      <x:c r="J28" s="529" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="K28" s="529" t="str">
+      <x:c r="J28" s="705" t="str">
+        <x:v>MSG-E-019／AUTH-4001</x:v>
+      </x:c>
+      <x:c r="K28" s="705" t="str">
         <x:v>Button／通信回数</x:v>
       </x:c>
-      <x:c r="L28" s="529" t="str">
+      <x:c r="L28" s="705" t="str">
         <x:v>05 STATE-003／06 EVT-002</x:v>
       </x:c>
     </x:row>
@@ -5141,15 +5204,29 @@
       <x:c r="C47" s="529"/>
       <x:c r="D47" s="529"/>
       <x:c r="E47" s="529" t="str">
-        <x:v>Header.Retry-After→STATE-006、未設定・不正値は60秒。待機中はFocus変更なし、0到達時にITEM-002 Focusを定義済み</x:v>
-      </x:c>
-      <x:c r="F47" s="529"/>
-      <x:c r="G47" s="529"/>
-      <x:c r="H47" s="529"/>
-      <x:c r="I47" s="529"/>
-      <x:c r="J47" s="529"/>
-      <x:c r="K47" s="529"/>
-      <x:c r="L47" s="529"/>
+        <x:v>Retry-Afterは非負整数。0有効・待機不要。不正値のみ60秒。正数待機中はFocus変更なし。0は再活性化後ITEM-002 Focus。</x:v>
+      </x:c>
+      <x:c r="F47" s="529" t="str">
+        <x:v>Retry-Afterは非負整数。0有効・待機不要。不正値のみ60秒。正数待機中はFocus変更なし。0は再活性化後ITEM-002 Focus。</x:v>
+      </x:c>
+      <x:c r="G47" s="529" t="str">
+        <x:v>Retry-Afterは非負整数。0有効・待機不要。不正値のみ60秒。正数待機中はFocus変更なし。0は再活性化後ITEM-002 Focus。</x:v>
+      </x:c>
+      <x:c r="H47" s="529" t="str">
+        <x:v>Retry-Afterは非負整数。0有効・待機不要。不正値のみ60秒。正数待機中はFocus変更なし。0は再活性化後ITEM-002 Focus。</x:v>
+      </x:c>
+      <x:c r="I47" s="529" t="str">
+        <x:v>Retry-Afterは非負整数。0有効・待機不要。不正値のみ60秒。正数待機中はFocus変更なし。0は再活性化後ITEM-002 Focus。</x:v>
+      </x:c>
+      <x:c r="J47" s="529" t="str">
+        <x:v>Retry-Afterは非負整数。0有効・待機不要。不正値のみ60秒。正数待機中はFocus変更なし。0は再活性化後ITEM-002 Focus。</x:v>
+      </x:c>
+      <x:c r="K47" s="529" t="str">
+        <x:v>Retry-Afterは非負整数。0有効・待機不要。不正値のみ60秒。正数待機中はFocus変更なし。0は再活性化後ITEM-002 Focus。</x:v>
+      </x:c>
+      <x:c r="L47" s="529" t="str">
+        <x:v>Retry-Afterは非負整数。0有効・待機不要。不正値のみ60秒。正数待機中はFocus変更なし。0は再活性化後ITEM-002 Focus。</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="42" customHeight="1">
       <x:c r="A48" s="529" t="n">
@@ -5181,35 +5258,67 @@
       <x:c r="C49" s="529"/>
       <x:c r="D49" s="529"/>
       <x:c r="E49" s="529" t="str">
-        <x:v>UT-001～034で主要正常・異常・型・強制変更・Focusを確認。実施結果は別途単体テスト仕様書に記録。</x:v>
-      </x:c>
-      <x:c r="F49" s="529"/>
-      <x:c r="G49" s="529"/>
-      <x:c r="H49" s="529"/>
-      <x:c r="I49" s="529"/>
-      <x:c r="J49" s="529"/>
-      <x:c r="K49" s="529"/>
-      <x:c r="L49" s="529"/>
+        <x:v>UT-001～038で主要経路、429境界、Button表示、Enter一回送信を確認。実施結果は別途単体テスト仕様書に記録。</x:v>
+      </x:c>
+      <x:c r="F49" s="529" t="str">
+        <x:v>UT-001～038で主要経路、429境界、Button表示、Enter一回送信を確認。実施結果は別途単体テスト仕様書に記録。</x:v>
+      </x:c>
+      <x:c r="G49" s="529" t="str">
+        <x:v>UT-001～038で主要経路、429境界、Button表示、Enter一回送信を確認。実施結果は別途単体テスト仕様書に記録。</x:v>
+      </x:c>
+      <x:c r="H49" s="529" t="str">
+        <x:v>UT-001～038で主要経路、429境界、Button表示、Enter一回送信を確認。実施結果は別途単体テスト仕様書に記録。</x:v>
+      </x:c>
+      <x:c r="I49" s="529" t="str">
+        <x:v>UT-001～038で主要経路、429境界、Button表示、Enter一回送信を確認。実施結果は別途単体テスト仕様書に記録。</x:v>
+      </x:c>
+      <x:c r="J49" s="529" t="str">
+        <x:v>UT-001～038で主要経路、429境界、Button表示、Enter一回送信を確認。実施結果は別途単体テスト仕様書に記録。</x:v>
+      </x:c>
+      <x:c r="K49" s="529" t="str">
+        <x:v>UT-001～038で主要経路、429境界、Button表示、Enter一回送信を確認。実施結果は別途単体テスト仕様書に記録。</x:v>
+      </x:c>
+      <x:c r="L49" s="529" t="str">
+        <x:v>UT-001～038で主要経路、429境界、Button表示、Enter一回送信を確認。実施結果は別途単体テスト仕様書に記録。</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="42" customHeight="1">
       <x:c r="A50" s="529" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B50" s="529" t="str">
-        <x:v>未確定表現</x:v>
-      </x:c>
-      <x:c r="C50" s="529"/>
-      <x:c r="D50" s="529"/>
+        <x:v>Message正本</x:v>
+      </x:c>
+      <x:c r="C50" s="529" t="str">
+        <x:v>Message正本</x:v>
+      </x:c>
+      <x:c r="D50" s="529" t="str">
+        <x:v>Message正本</x:v>
+      </x:c>
       <x:c r="E50" s="529" t="str">
-        <x:v>未採番Messageは既存MSG-Vへ解決。参照BaselineはBL-2026-09-24。</x:v>
-      </x:c>
-      <x:c r="F50" s="529"/>
-      <x:c r="G50" s="529"/>
-      <x:c r="H50" s="529"/>
-      <x:c r="I50" s="529"/>
-      <x:c r="J50" s="529"/>
-      <x:c r="K50" s="529"/>
-      <x:c r="L50" s="529"/>
+        <x:v>項目Validation Messageは18_メッセージと例外_基本設計書／31V_ValidationMessageのMSG-V定義・Parameterに従う。</x:v>
+      </x:c>
+      <x:c r="F50" s="529" t="str">
+        <x:v>項目Validation Messageは18_メッセージと例外_基本設計書／31V_ValidationMessageのMSG-V定義・Parameterに従う。</x:v>
+      </x:c>
+      <x:c r="G50" s="529" t="str">
+        <x:v>項目Validation Messageは18_メッセージと例外_基本設計書／31V_ValidationMessageのMSG-V定義・Parameterに従う。</x:v>
+      </x:c>
+      <x:c r="H50" s="529" t="str">
+        <x:v>項目Validation Messageは18_メッセージと例外_基本設計書／31V_ValidationMessageのMSG-V定義・Parameterに従う。</x:v>
+      </x:c>
+      <x:c r="I50" s="529" t="str">
+        <x:v>項目Validation Messageは18_メッセージと例外_基本設計書／31V_ValidationMessageのMSG-V定義・Parameterに従う。</x:v>
+      </x:c>
+      <x:c r="J50" s="529" t="str">
+        <x:v>項目Validation Messageは18_メッセージと例外_基本設計書／31V_ValidationMessageのMSG-V定義・Parameterに従う。</x:v>
+      </x:c>
+      <x:c r="K50" s="529" t="str">
+        <x:v>項目Validation Messageは18_メッセージと例外_基本設計書／31V_ValidationMessageのMSG-V定義・Parameterに従う。</x:v>
+      </x:c>
+      <x:c r="L50" s="529" t="str">
+        <x:v>項目Validation Messageは18_メッセージと例外_基本設計書／31V_ValidationMessageのMSG-V定義・Parameterに従う。</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="42" customHeight="1">
       <x:c r="A51" s="529" t="n">
@@ -5487,61 +5596,157 @@
         <x:v>03／21_ValidationLifecycle VC-008；06 Step13/14</x:v>
       </x:c>
     </x:row>
-    <x:row r="60">
-      <x:c r="A60" s="242"/>
-      <x:c r="B60" s="242"/>
-      <x:c r="C60" s="242"/>
-      <x:c r="D60" s="242"/>
-      <x:c r="E60" s="242"/>
-      <x:c r="F60" s="242"/>
-      <x:c r="G60" s="242"/>
-      <x:c r="H60" s="242"/>
-      <x:c r="I60" s="242"/>
-      <x:c r="J60" s="242"/>
-      <x:c r="K60" s="242"/>
-      <x:c r="L60" s="242"/>
-    </x:row>
-    <x:row r="61">
-      <x:c r="A61" s="242"/>
-      <x:c r="B61" s="242"/>
-      <x:c r="C61" s="242"/>
-      <x:c r="D61" s="242"/>
-      <x:c r="E61" s="242"/>
-      <x:c r="F61" s="242"/>
-      <x:c r="G61" s="242"/>
-      <x:c r="H61" s="242"/>
-      <x:c r="I61" s="242"/>
-      <x:c r="J61" s="242"/>
-      <x:c r="K61" s="242"/>
-      <x:c r="L61" s="242"/>
-    </x:row>
-    <x:row r="62">
-      <x:c r="A62" s="242"/>
-      <x:c r="B62" s="242"/>
-      <x:c r="C62" s="242"/>
-      <x:c r="D62" s="242"/>
-      <x:c r="E62" s="242"/>
-      <x:c r="F62" s="242"/>
-      <x:c r="G62" s="242"/>
-      <x:c r="H62" s="242"/>
-      <x:c r="I62" s="242"/>
-      <x:c r="J62" s="242"/>
-      <x:c r="K62" s="242"/>
-      <x:c r="L62" s="242"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="242"/>
-      <x:c r="B63" s="242"/>
-      <x:c r="C63" s="242"/>
-      <x:c r="D63" s="242"/>
-      <x:c r="E63" s="242"/>
-      <x:c r="F63" s="242"/>
-      <x:c r="G63" s="242"/>
-      <x:c r="H63" s="242"/>
-      <x:c r="I63" s="242"/>
-      <x:c r="J63" s="242"/>
-      <x:c r="K63" s="242"/>
-      <x:c r="L63" s="242"/>
+    <x:row r="60" ht="145" customHeight="1">
+      <x:c r="A60" s="242" t="str">
+        <x:v>UT-035</x:v>
+      </x:c>
+      <x:c r="B60" s="242" t="str">
+        <x:v>CONTROL</x:v>
+      </x:c>
+      <x:c r="C60" s="242" t="str">
+        <x:v>EVT-002 Step12／STATE-006</x:v>
+      </x:c>
+      <x:c r="D60" s="242" t="str">
+        <x:v>user01 / ValidPass1入力済、STATE-004=false</x:v>
+      </x:c>
+      <x:c r="E60" s="242" t="str">
+        <x:v>Login後に429を返す</x:v>
+      </x:c>
+      <x:c r="F60" s="242" t="str">
+        <x:v>AUTH-001=429 / AUTH-4290、Retry-After: 0</x:v>
+      </x:c>
+      <x:c r="G60" s="242" t="str">
+        <x:v>MSG-E-008[0]。入力とButton即時再活性化、ITEM-002 Focus、表示「ログイン」</x:v>
+      </x:c>
+      <x:c r="H60" s="242" t="str">
+        <x:v>STATE-006=0、STATE-003=false、username保持、password空。60秒Fallback・Timer開始なし</x:v>
+      </x:c>
+      <x:c r="I60" s="242" t="str">
+        <x:v>SCR-001、Password再入力後に再Login可能</x:v>
+      </x:c>
+      <x:c r="J60" s="242" t="str">
+        <x:v>MSG-E-008／AUTH-4290</x:v>
+      </x:c>
+      <x:c r="K60" s="242" t="str">
+        <x:v>DOM／State／Timer未起動／Focus</x:v>
+      </x:c>
+      <x:c r="L60" s="242" t="str">
+        <x:v>06 Step12／07 Header／08 No.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="145" customHeight="1">
+      <x:c r="A61" s="242" t="str">
+        <x:v>UT-036</x:v>
+      </x:c>
+      <x:c r="B61" s="242" t="str">
+        <x:v>CONTROL</x:v>
+      </x:c>
+      <x:c r="C61" s="242" t="str">
+        <x:v>EVT-002 Step12／STATE-006</x:v>
+      </x:c>
+      <x:c r="D61" s="242" t="str">
+        <x:v>user01 / ValidPass1入力済</x:v>
+      </x:c>
+      <x:c r="E61" s="242" t="str">
+        <x:v>各Header条件を独立実行</x:v>
+      </x:c>
+      <x:c r="F61" s="242" t="str">
+        <x:v>429、Header：欠落／空／abc／-1／1.5／1e2</x:v>
+      </x:c>
+      <x:c r="G61" s="242" t="str">
+        <x:v>MSG-E-008[60]。ITEM-001～003 disabled、Focus指定なし</x:v>
+      </x:c>
+      <x:c r="H61" s="242" t="str">
+        <x:v>STATE-006=60、STATE-003=false。60秒経過後0・再活性化後ITEM-002 Focus</x:v>
+      </x:c>
+      <x:c r="I61" s="242" t="str">
+        <x:v>SCR-001</x:v>
+      </x:c>
+      <x:c r="J61" s="242" t="str">
+        <x:v>MSG-E-008／AUTH-4290</x:v>
+      </x:c>
+      <x:c r="K61" s="242" t="str">
+        <x:v>各条件のMock／Fake Timer／DOM</x:v>
+      </x:c>
+      <x:c r="L61" s="242" t="str">
+        <x:v>06 Step12／07 Header</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="145" customHeight="1">
+      <x:c r="A62" s="242" t="str">
+        <x:v>UT-037</x:v>
+      </x:c>
+      <x:c r="B62" s="242" t="str">
+        <x:v>EVENT</x:v>
+      </x:c>
+      <x:c r="C62" s="242" t="str">
+        <x:v>ITEM-003／EVT-002</x:v>
+      </x:c>
+      <x:c r="D62" s="242" t="str">
+        <x:v>username=user01、password=ValidPass1、STATE-003=false、STATE-004=false、STATE-006=0</x:v>
+      </x:c>
+      <x:c r="E62" s="242" t="str">
+        <x:v>Password欄でEnter。AUTH-001保留中にもう一度Enter</x:v>
+      </x:c>
+      <x:c r="F62" s="242" t="str">
+        <x:v>AUTH-001=200後AUTH-004=200、passwordMustChange=false、redirectなし</x:v>
+      </x:c>
+      <x:c r="G62" s="242" t="str">
+        <x:v>送信中は「ログイン中…」・disabled。通常画面へ遷移</x:v>
+      </x:c>
+      <x:c r="H62" s="242" t="str">
+        <x:v>EVT-002の実行可判定後、AUTH-001とAUTH-004は各1回。二重Submitなし</x:v>
+      </x:c>
+      <x:c r="I62" s="242" t="str">
+        <x:v>SCR-002 /home</x:v>
+      </x:c>
+      <x:c r="J62" s="242" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="K62" s="242" t="str">
+        <x:v>Keyboard／通信回数／State／Route</x:v>
+      </x:c>
+      <x:c r="L62" s="242" t="str">
+        <x:v>04 ITEM-003／06 Step1・4～10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="145" customHeight="1">
+      <x:c r="A63" s="242" t="str">
+        <x:v>UT-038</x:v>
+      </x:c>
+      <x:c r="B63" s="242" t="str">
+        <x:v>CONTROL</x:v>
+      </x:c>
+      <x:c r="C63" s="242" t="str">
+        <x:v>EVT-002 Step12／STATE-006</x:v>
+      </x:c>
+      <x:c r="D63" s="242" t="str">
+        <x:v>user01 / ValidPass1入力済</x:v>
+      </x:c>
+      <x:c r="E63" s="242" t="str">
+        <x:v>429受信後Timerを1秒進める</x:v>
+      </x:c>
+      <x:c r="F63" s="242" t="str">
+        <x:v>429 / AUTH-4290、Retry-After: 1</x:v>
+      </x:c>
+      <x:c r="G63" s="242" t="str">
+        <x:v>直後disabled・Focus変更なし。1秒後enabled・ITEM-002 Focus</x:v>
+      </x:c>
+      <x:c r="H63" s="242" t="str">
+        <x:v>STATE-006：1→0、STATE-003=false。Timer終了。Button表示「ログイン」</x:v>
+      </x:c>
+      <x:c r="I63" s="242" t="str">
+        <x:v>SCR-001</x:v>
+      </x:c>
+      <x:c r="J63" s="242" t="str">
+        <x:v>MSG-E-008／AUTH-4290</x:v>
+      </x:c>
+      <x:c r="K63" s="242" t="str">
+        <x:v>Fake Timer／State／DOM／Focus</x:v>
+      </x:c>
+      <x:c r="L63" s="242" t="str">
+        <x:v>06 Step12／07 Header／08 No.9</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="242"/>
@@ -6222,10 +6427,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="69" t="str">
-        <x:v>Ver.2.3</x:v>
-      </x:c>
-      <x:c r="K2" s="69"/>
-      <x:c r="L2" s="69"/>
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="K2" s="69" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="L2" s="69" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="70"/>
@@ -6443,19 +6652,29 @@
       <x:c r="K12" s="2"/>
       <x:c r="L12" s="2"/>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13"/>
-      <x:c r="B13"/>
-      <x:c r="C13"/>
-      <x:c r="D13"/>
-      <x:c r="E13"/>
-      <x:c r="F13"/>
-      <x:c r="G13"/>
-      <x:c r="H13"/>
-      <x:c r="I13" s="2"/>
-      <x:c r="J13" s="2"/>
-      <x:c r="K13" s="2"/>
-      <x:c r="L13" s="2"/>
+    <x:row r="13" ht="105" customHeight="1">
+      <x:c r="A13" s="242" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="B13" s="242" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="C13" s="242" t="str">
+        <x:v>改訂</x:v>
+      </x:c>
+      <x:c r="D13" s="242" t="str">
+        <x:v>Retry-After=0、Navigation記述、Validation参照、Button／Enter単体テストを修正。CHG-AUTH-20260928-01</x:v>
+      </x:c>
+      <x:c r="E13" s="242" t="str"/>
+      <x:c r="F13" s="242" t="str"/>
+      <x:c r="G13" s="242" t="str"/>
+      <x:c r="H13" s="242" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="I13" s="111"/>
+      <x:c r="J13" s="111"/>
+      <x:c r="K13" s="111"/>
+      <x:c r="L13" s="111"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14"/>
@@ -6687,10 +6906,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.3</x:v>
-      </x:c>
-      <x:c r="K2" s="80"/>
-      <x:c r="L2" s="80"/>
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="K2" s="80" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="L2" s="80" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="241"/>
@@ -8290,10 +8513,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.3</x:v>
-      </x:c>
-      <x:c r="K2" s="80"/>
-      <x:c r="L2" s="80"/>
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="K2" s="80" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="L2" s="80" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="241"/>
@@ -9946,10 +10173,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.3</x:v>
-      </x:c>
-      <x:c r="K2" s="80"/>
-      <x:c r="L2" s="80"/>
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="K2" s="80" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="L2" s="80" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="241"/>
@@ -11598,10 +11829,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.3</x:v>
-      </x:c>
-      <x:c r="K2" s="80"/>
-      <x:c r="L2" s="80"/>
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="K2" s="80" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="L2" s="80" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="241"/>
@@ -12160,7 +12395,7 @@
         <x:v>ITEM-001～003／AUTH-4290</x:v>
       </x:c>
       <x:c r="L26" s="529" t="str">
-        <x:v>Retry-After Headerを秒へ変換。未設定・不正値は60</x:v>
+        <x:v>10進非負整数秒。0は待機不要。未設定・空・非整数・負数は60。07 Mappingに従う。</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="54" hidden="0" customHeight="1">
@@ -13216,10 +13451,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.3</x:v>
-      </x:c>
-      <x:c r="K2" s="80"/>
-      <x:c r="L2" s="80"/>
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="K2" s="80" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="L2" s="80" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="241"/>
@@ -14010,7 +14249,7 @@
         <x:v>END</x:v>
       </x:c>
       <x:c r="J38" s="529" t="str">
-        <x:v>共通Navigation Error</x:v>
+        <x:v>－</x:v>
       </x:c>
       <x:c r="K38" s="529" t="str">
         <x:v>STATE-007／008／SCR-026／SCR-002</x:v>
@@ -14644,10 +14883,14 @@
       </x:c>
       <x:c r="C63" s="529"/>
       <x:c r="D63" s="529" t="str">
-        <x:v>STATE-003=trueとし、ITEM-001～003を非活性化する</x:v>
-      </x:c>
-      <x:c r="E63" s="529"/>
-      <x:c r="F63" s="529"/>
+        <x:v>STATE-003=trueとしITEM-001～003を非活性化する。ITEM-003は「ログイン中…」を表示する。</x:v>
+      </x:c>
+      <x:c r="E63" s="529" t="str">
+        <x:v>STATE-003=trueとしITEM-001～003を非活性化する。ITEM-003は「ログイン中…」を表示する。</x:v>
+      </x:c>
+      <x:c r="F63" s="529" t="str">
+        <x:v>STATE-003=trueとしITEM-001～003を非活性化する。ITEM-003は「ログイン中…」を表示する。</x:v>
+      </x:c>
       <x:c r="G63" s="529" t="str">
         <x:v>Validation正常</x:v>
       </x:c>
@@ -14836,7 +15079,7 @@
         <x:v>END</x:v>
       </x:c>
       <x:c r="J69" s="529" t="str">
-        <x:v>共通Navigation Error</x:v>
+        <x:v>－</x:v>
       </x:c>
       <x:c r="K69" s="529" t="str">
         <x:v>STATE-007／008／SCR-026／SCR-002</x:v>
@@ -14875,34 +15118,38 @@
         <x:v>SCR-001に留まる</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="54" customHeight="1">
-      <x:c r="A71" s="529" t="n">
+    <x:row r="71" ht="205" customHeight="1">
+      <x:c r="A71" s="705" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B71" s="529" t="str">
+      <x:c r="B71" s="705" t="str">
         <x:v>再試行制御</x:v>
       </x:c>
-      <x:c r="C71" s="529"/>
-      <x:c r="D71" s="529" t="str">
-        <x:v>Retry-After Headerを正の整数秒へ変換してSTATE-006へ設定する。Headerが未設定または不正値の場合は60とする。STATE-003=falseとしてITEM-001～003を非活性のままCount Downを開始し、発生直後はFocusを変更しない。STATE-006=0到達時にITEM-001～003を再活性化してITEM-002へFocusする</x:v>
-      </x:c>
-      <x:c r="E71" s="529"/>
-      <x:c r="F71" s="529"/>
-      <x:c r="G71" s="529" t="str">
+      <x:c r="C71" s="705"/>
+      <x:c r="D71" s="705" t="str">
+        <x:v>Retry-Afterを10進非負整数として解析しSTATE-006へ設定する。未設定・空・整数変換不可・負数のみ60秒を使用。STATE-003=falseとしButton表示を「ログイン」に戻す。値&gt;0はITEM-001～003非活性のままCount DownしFocus変更なし。初期値0はTimerを開始しない。0到達／初期値0の双方でITEM-001～003を再活性化し、画面反映後ITEM-002へFocusする。</x:v>
+      </x:c>
+      <x:c r="E71" s="705" t="str">
+        <x:v>Retry-Afterを10進非負整数として解析しSTATE-006へ設定する。未設定・空・整数変換不可・負数のみ60秒を使用。STATE-003=falseとしButton表示を「ログイン」に戻す。値&gt;0はITEM-001～003非活性のままCount DownしFocus変更なし。初期値0はTimerを開始しない。0到達／初期値0の双方でITEM-001～003を再活性化し、画面反映後ITEM-002へFocusする。</x:v>
+      </x:c>
+      <x:c r="F71" s="705" t="str">
+        <x:v>Retry-Afterを10進非負整数として解析しSTATE-006へ設定する。未設定・空・整数変換不可・負数のみ60秒を使用。STATE-003=falseとしButton表示を「ログイン」に戻す。値&gt;0はITEM-001～003非活性のままCount DownしFocus変更なし。初期値0はTimerを開始しない。0到達／初期値0の双方でITEM-001～003を再活性化し、画面反映後ITEM-002へFocusする。</x:v>
+      </x:c>
+      <x:c r="G71" s="705" t="str">
         <x:v>AUTH-4290</x:v>
       </x:c>
-      <x:c r="H71" s="529"/>
-      <x:c r="I71" s="529" t="str">
-        <x:v>Count Down終了:END</x:v>
-      </x:c>
-      <x:c r="J71" s="529" t="str">
+      <x:c r="H71" s="705"/>
+      <x:c r="I71" s="705" t="str">
+        <x:v>初期値0：即時END／正数：0到達後END</x:v>
+      </x:c>
+      <x:c r="J71" s="705" t="str">
         <x:v>―</x:v>
       </x:c>
-      <x:c r="K71" s="529" t="str">
+      <x:c r="K71" s="705" t="str">
         <x:v>STATE-003／006／ITEM-001～003／AUTH-4290／MSG-E-008</x:v>
       </x:c>
-      <x:c r="L71" s="529" t="str">
-        <x:v>待機中は操作不可。終了後は再操作可能</x:v>
+      <x:c r="L71" s="705" t="str">
+        <x:v>0秒なら待機なしで再Login可。正数は待機終了後に再操作可。</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="54" customHeight="1">
@@ -14944,10 +15191,14 @@
       </x:c>
       <x:c r="C73" s="529"/>
       <x:c r="D73" s="529" t="str">
-        <x:v>STATE-003=falseとしITEM-001～003を再活性化する。活性状態の画面反映後に08の対象Errorで指定したITEMへFocusする。AUTH-4290はStep12で処理する。</x:v>
-      </x:c>
-      <x:c r="E73" s="529"/>
-      <x:c r="F73" s="529"/>
+        <x:v>STATE-003=falseとしITEM-003表示を「ログイン」へ戻す。ITEM-001～003再活性化の画面反映後に08の指定ITEMへFocusする。AUTH-4290はStep12で処理する。</x:v>
+      </x:c>
+      <x:c r="E73" s="529" t="str">
+        <x:v>STATE-003=falseとしITEM-003表示を「ログイン」へ戻す。ITEM-001～003再活性化の画面反映後に08の指定ITEMへFocusする。AUTH-4290はStep12で処理する。</x:v>
+      </x:c>
+      <x:c r="F73" s="529" t="str">
+        <x:v>STATE-003=falseとしITEM-003表示を「ログイン」へ戻す。ITEM-001～003再活性化の画面反映後に08の指定ITEMへFocusする。AUTH-4290はStep12で処理する。</x:v>
+      </x:c>
       <x:c r="G73" s="529" t="str">
         <x:v>AUTH-4290以外の異常でSCR-001表示中</x:v>
       </x:c>
@@ -15732,10 +15983,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.3</x:v>
-      </x:c>
-      <x:c r="K2" s="80"/>
-      <x:c r="L2" s="80"/>
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="K2" s="80" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="L2" s="80" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="241"/>
@@ -16617,32 +16872,32 @@
       <x:c r="K42" s="111"/>
       <x:c r="L42" s="111"/>
     </x:row>
-    <x:row r="43" ht="48" hidden="0" customHeight="1">
-      <x:c r="A43" s="529" t="n">
+    <x:row r="43" ht="120" hidden="0" customHeight="1">
+      <x:c r="A43" s="705" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B43" s="529" t="str">
+      <x:c r="B43" s="705" t="str">
         <x:v>API-AUTH-001</x:v>
       </x:c>
-      <x:c r="C43" s="529" t="str">
+      <x:c r="C43" s="705" t="str">
         <x:v>Header.Retry-After</x:v>
       </x:c>
-      <x:c r="D43" s="529" t="str">
+      <x:c r="D43" s="705" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="E43" s="529" t="str">
+      <x:c r="E43" s="705" t="str">
         <x:v>STATE-006</x:v>
       </x:c>
-      <x:c r="F43" s="529" t="str">
-        <x:v>10進数の正の整数秒へ変換する</x:v>
-      </x:c>
-      <x:c r="G43" s="529" t="str">
-        <x:v>未設定・空・数値変換不可・0以下の場合は60</x:v>
-      </x:c>
-      <x:c r="H43" s="529" t="str">
-        <x:v>AUTH-4290発生時の再試行待機時間</x:v>
-      </x:c>
-      <x:c r="I43" s="529" t="str">
+      <x:c r="F43" s="705" t="str">
+        <x:v>10進数字のみの非負整数秒として解析。0は有効（待機なし）。小数・指数表記・HTTP-dateは整数形式不正。</x:v>
+      </x:c>
+      <x:c r="G43" s="705" t="str">
+        <x:v>未設定・空・整数変換不可・負数のみ60。0はFallbackしない。</x:v>
+      </x:c>
+      <x:c r="H43" s="705" t="str">
+        <x:v>429の待機時間。0なら即時再活性化後ITEM-002 Focus。</x:v>
+      </x:c>
+      <x:c r="I43" s="705" t="str">
         <x:v>EVT-002 Step12</x:v>
       </x:c>
       <x:c r="J43" s="111"/>
@@ -16754,7 +17009,7 @@
         <x:v>401 / AUTH-4001</x:v>
       </x:c>
       <x:c r="D48" s="529" t="str">
-        <x:v>ユーザー名またはパスワード不一致</x:v>
+        <x:v>User不存在、またはLock未成立のPassword不一致（連続1～4回）</x:v>
       </x:c>
       <x:c r="E48" s="529" t="str">
         <x:v>EVT-002 Step11</x:v>
@@ -16766,7 +17021,7 @@
         <x:v>08 No.5参照。入力・Session・Focusの正本は08。</x:v>
       </x:c>
       <x:c r="H48" s="529" t="str">
-        <x:v>08の最終状態に従う。通常Errorは再活性化後Focus、429はCount Down終了後。</x:v>
+        <x:v>08の最終状態に従う。429は待機終了／初期値0の再活性化後にFocus。</x:v>
       </x:c>
       <x:c r="I48" s="529" t="str">
         <x:v>08 No.5</x:v>
@@ -16786,7 +17041,7 @@
         <x:v>423 / AUTH-4004</x:v>
       </x:c>
       <x:c r="D49" s="529" t="str">
-        <x:v>アカウントロック</x:v>
+        <x:v>第5回失敗によるLock成立、またはLock期間中</x:v>
       </x:c>
       <x:c r="E49" s="529" t="str">
         <x:v>EVT-002 Step11</x:v>
@@ -16798,7 +17053,7 @@
         <x:v>08 No.6参照。入力・Session・Focusの正本は08。</x:v>
       </x:c>
       <x:c r="H49" s="529" t="str">
-        <x:v>08の最終状態に従う。通常Errorは再活性化後Focus、429はCount Down終了後。</x:v>
+        <x:v>08の最終状態に従う。429は待機終了／初期値0の再活性化後にFocus。</x:v>
       </x:c>
       <x:c r="I49" s="529" t="str">
         <x:v>08 No.6</x:v>
@@ -16830,7 +17085,7 @@
         <x:v>08 No.7参照。入力・Session・Focusの正本は08。</x:v>
       </x:c>
       <x:c r="H50" s="529" t="str">
-        <x:v>08の最終状態に従う。通常Errorは再活性化後Focus、429はCount Down終了後。</x:v>
+        <x:v>08の最終状態に従う。429は待機終了／初期値0の再活性化後にFocus。</x:v>
       </x:c>
       <x:c r="I50" s="529" t="str">
         <x:v>08 No.7</x:v>
@@ -16862,7 +17117,7 @@
         <x:v>08 No.9参照。入力・Session・Focusの正本は08。</x:v>
       </x:c>
       <x:c r="H51" s="529" t="str">
-        <x:v>08の最終状態に従う。通常Errorは再活性化後Focus、429はCount Down終了後。</x:v>
+        <x:v>08の最終状態に従う。429は待機終了／初期値0の再活性化後にFocus。</x:v>
       </x:c>
       <x:c r="I51" s="529" t="str">
         <x:v>08 No.9</x:v>
@@ -16894,7 +17149,7 @@
         <x:v>08 No.11参照。入力・Session・Focusの正本は08。</x:v>
       </x:c>
       <x:c r="H52" s="529" t="str">
-        <x:v>08の最終状態に従う。通常Errorは再活性化後Focus、429はCount Down終了後。</x:v>
+        <x:v>08の最終状態に従う。429は待機終了／初期値0の再活性化後にFocus。</x:v>
       </x:c>
       <x:c r="I52" s="529" t="str">
         <x:v>08 No.11</x:v>
@@ -16926,7 +17181,7 @@
         <x:v>08 No.12参照。入力・Session・Focusの正本は08。</x:v>
       </x:c>
       <x:c r="H53" s="529" t="str">
-        <x:v>08の最終状態に従う。通常Errorは再活性化後Focus、429はCount Down終了後。</x:v>
+        <x:v>08の最終状態に従う。429は待機終了／初期値0の再活性化後にFocus。</x:v>
       </x:c>
       <x:c r="I53" s="529" t="str">
         <x:v>08 No.12</x:v>
@@ -16958,7 +17213,7 @@
         <x:v>08 No.10参照。入力・Session・Focusの正本は08。</x:v>
       </x:c>
       <x:c r="H54" s="529" t="str">
-        <x:v>08の最終状態に従う。通常Errorは再活性化後Focus、429はCount Down終了後。</x:v>
+        <x:v>08の最終状態に従う。429は待機終了／初期値0の再活性化後にFocus。</x:v>
       </x:c>
       <x:c r="I54" s="529" t="str">
         <x:v>08 No.10</x:v>
@@ -16990,7 +17245,7 @@
         <x:v>08 No.8参照。入力・Session・Focusの正本は08。</x:v>
       </x:c>
       <x:c r="H55" s="529" t="str">
-        <x:v>08の最終状態に従う。通常Errorは再活性化後Focus、429はCount Down終了後。</x:v>
+        <x:v>08の最終状態に従う。429は待機終了／初期値0の再活性化後にFocus。</x:v>
       </x:c>
       <x:c r="I55" s="529" t="str">
         <x:v>08 No.8</x:v>
@@ -17022,7 +17277,7 @@
         <x:v>08 No.11参照。入力・Session・Focusの正本は08。</x:v>
       </x:c>
       <x:c r="H56" s="529" t="str">
-        <x:v>08の最終状態に従う。通常Errorは再活性化後Focus、429はCount Down終了後。</x:v>
+        <x:v>08の最終状態に従う。429は待機終了／初期値0の再活性化後にFocus。</x:v>
       </x:c>
       <x:c r="I56" s="529" t="str">
         <x:v>08 No.11</x:v>
@@ -17054,7 +17309,7 @@
         <x:v>08 No.12参照。入力・Session・Focusの正本は08。</x:v>
       </x:c>
       <x:c r="H57" s="529" t="str">
-        <x:v>08の最終状態に従う。通常Errorは再活性化後Focus、429はCount Down終了後。</x:v>
+        <x:v>08の最終状態に従う。429は待機終了／初期値0の再活性化後にFocus。</x:v>
       </x:c>
       <x:c r="I57" s="529" t="str">
         <x:v>08 No.12</x:v>
@@ -17942,10 +18197,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.3</x:v>
-      </x:c>
-      <x:c r="K2" s="80"/>
-      <x:c r="L2" s="80"/>
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="K2" s="80" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="L2" s="80" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="241"/>
@@ -18261,7 +18520,7 @@
         <x:v>EVT-002 Step11</x:v>
       </x:c>
       <x:c r="E14" s="529" t="str">
-        <x:v>ユーザー名またはパスワード不一致</x:v>
+        <x:v>User不存在、またはPassword連続失敗1～4回</x:v>
       </x:c>
       <x:c r="F14" s="529" t="str">
         <x:v>画面上部</x:v>
@@ -18299,7 +18558,7 @@
         <x:v>EVT-002 Step11</x:v>
       </x:c>
       <x:c r="E15" s="529" t="str">
-        <x:v>アカウントロック</x:v>
+        <x:v>Password連続失敗5回目、またはLock期間中</x:v>
       </x:c>
       <x:c r="F15" s="529" t="str">
         <x:v>画面上部</x:v>
@@ -18399,41 +18658,41 @@
         <x:v>18／31B_ErrorMessage対応（対象API別）</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="100" hidden="0" customHeight="1">
-      <x:c r="A18" s="529" t="n">
+    <x:row r="18" ht="135" hidden="0" customHeight="1">
+      <x:c r="A18" s="705" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B18" s="529" t="str">
+      <x:c r="B18" s="705" t="str">
         <x:v>Business</x:v>
       </x:c>
-      <x:c r="C18" s="529" t="str">
+      <x:c r="C18" s="705" t="str">
         <x:v>MSG-E-008／AUTH-4290</x:v>
       </x:c>
-      <x:c r="D18" s="529" t="str">
+      <x:c r="D18" s="705" t="str">
         <x:v>EVT-002 Step11／12（API-AUTH-001）</x:v>
       </x:c>
-      <x:c r="E18" s="529" t="str">
+      <x:c r="E18" s="705" t="str">
         <x:v>1分間の試行回数超過</x:v>
       </x:c>
-      <x:c r="F18" s="529" t="str">
+      <x:c r="F18" s="705" t="str">
         <x:v>画面上部</x:v>
       </x:c>
-      <x:c r="G18" s="529" t="str">
+      <x:c r="G18" s="705" t="str">
         <x:v>18／31_メッセージ MSG-E-008、Parameter=[Retry-After秒]。秒数はSTATE-006の初期設定値。</x:v>
       </x:c>
-      <x:c r="H18" s="529" t="str">
-        <x:v>STATE-001保持、STATE-002クリア、STATE-006設定</x:v>
-      </x:c>
-      <x:c r="I18" s="529" t="str">
-        <x:v>発生直後：Focus変更なし／Count Down終了時：ITEM-002</x:v>
-      </x:c>
-      <x:c r="J18" s="529" t="str">
-        <x:v>STATE-006&gt;0はITEM-001～003非活性。0到達時に再活性化</x:v>
-      </x:c>
-      <x:c r="K18" s="529" t="str">
+      <x:c r="H18" s="705" t="str">
+        <x:v>STATE-001保持、STATE-002クリア、STATE-006は07の解析値。0を60へ置換しない。</x:v>
+      </x:c>
+      <x:c r="I18" s="705" t="str">
+        <x:v>正数待機中：Focus変更なし。初期値0／0到達時：再活性化の画面反映後ITEM-002。</x:v>
+      </x:c>
+      <x:c r="J18" s="705" t="str">
+        <x:v>STATE-003=false、表示「ログイン」。STATE-006&gt;0は非活性。0は即時／到達時にITEM-001～003再活性化。</x:v>
+      </x:c>
+      <x:c r="K18" s="705" t="str">
         <x:v>SCR-001に留まる</x:v>
       </x:c>
-      <x:c r="L18" s="529" t="str">
+      <x:c r="L18" s="705" t="str">
         <x:v>18_メッセージと例外／MSG-E-008</x:v>
       </x:c>
     </x:row>

--- a/詳細設計/画面詳細設計/01_SCR-001_ログイン画面詳細設計書_React.xlsx
+++ b/詳細設計/画面詳細設計/01_SCR-001_ログイン画面詳細設計書_React.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rb3ff751f98324b88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Ra713412ff8264d5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_画面概要" sheetId="3" r:id="R5ae780e457f4443e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_画面レイアウト" sheetId="4" r:id="R171af198e2154e3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_画面項目" sheetId="5" r:id="R37cd7aaf898545ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Component_State" sheetId="6" r:id="R354d20bef5d649b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Event処理" sheetId="7" r:id="Rd2374e67b1e54c0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_API_Mapping" sheetId="8" r:id="R2f36e49c669344f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Message_例外" sheetId="9" r:id="R486eb63b9c1747a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_単体テスト観点" sheetId="10" r:id="R18ef82a3d2114434"/>
-  </x:sheets>
-</x:workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheets>
+    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="Rc7806f27c0ea4791"/>
+    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="R29264a1decdd4084"/>
+    <ns0:sheet name="02_画面概要" sheetId="3" ns1:id="R4f86f793e7ce4353"/>
+    <ns0:sheet name="03_画面レイアウト" sheetId="4" ns1:id="R1b401617af2942de"/>
+    <ns0:sheet name="04_画面項目" sheetId="5" ns1:id="Rc28523823f7f451f"/>
+    <ns0:sheet name="05_Component_State" sheetId="6" ns1:id="R32a08b7872be4749"/>
+    <ns0:sheet name="06_Event処理" sheetId="7" ns1:id="R12c58aef70d74c94"/>
+    <ns0:sheet name="07_API_Mapping" sheetId="8" ns1:id="Rb47a07ec5eb145b1"/>
+    <ns0:sheet name="08_Message_例外" sheetId="9" ns1:id="R3d856f5d82e04a7d"/>
+    <ns0:sheet name="09_単体テスト観点" sheetId="10" ns1:id="R485988af67d74eb1"/>
+  </ns0:sheets>
+</ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3189,7 +3189,7 @@
       <x:c r="H2" s="2"/>
       <x:c r="I2" s="2"/>
       <x:c r="J2" s="2" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="2"/>
       <x:c r="L2" s="2"/>
@@ -3379,7 +3379,7 @@
       <x:c r="D15" s="36"/>
       <x:c r="E15" s="36"/>
       <x:c r="F15" s="38" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="G15" s="38" t="str">
         <x:v>Ver.2.4</x:v>
@@ -3494,7 +3494,7 @@
     </x:row>
     <x:row r="22" ht="44" customHeight="1">
       <x:c r="A22" s="58" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01＋CHG-MENU-20260929-01（02 Ver.2.6・10 Ver.2.7）。menus契約・Mockを同期。既存Login処理・権限は変更なし。正式承認は別途記録。</x:v>
       </x:c>
       <x:c r="B22" s="59" t="str">
         <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
@@ -3763,7 +3763,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
         <x:v>Ver.2.4</x:v>
@@ -5520,7 +5520,7 @@
         <x:v>07行54；08 No.10</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="160" customHeight="1">
+    <x:row r="58" ht="285" customHeight="1">
       <x:c r="A58" s="704" t="str">
         <x:v>UT-033</x:v>
       </x:c>
@@ -5537,13 +5537,13 @@
         <x:v>/loginを表示</x:v>
       </x:c>
       <x:c r="F58" s="704" t="str">
-        <x:v>200：user.id=1、employeeId=1001（数値）、name=社員A、roles=[EMP]、permissions=[]、menus=[]、passwordMustChange=false。共通Envelopeは契約どおり</x:v>
+        <x:v>200：user.id=1、employeeId=1001（数値）、name=社員A、roles=[ROLE-EMP]、permissions=["PERM-DASH-READ","PERM-PRJ-READ","PERM-TASK-READ","PERM-TASK-PROGRESS","PERM-RPT-SELF","PERM-FILE-WRITE"]、menus=["MENU-HOME","MENU-PROJECTS","MENU-MY-PROJECTS","MENU-MY-TASKS","MENU-TASK-BOARD","MENU-MY-REPORTS","MENU-NOTIFICATIONS"]、passwordMustChange=false。Envelopeは契約どおり。</x:v>
       </x:c>
       <x:c r="G58" s="704" t="str">
         <x:v>Schema Errorなし</x:v>
       </x:c>
       <x:c r="H58" s="704" t="str">
-        <x:v>employeeIdは数値、menusはstring[]として保存。余分な変換なし</x:v>
+        <x:v>employeeIdは数値。menusは受信した固定Code配列としてSTATE-008へ保存し、表示名へ変換しない。共通01 S022へ渡す。</x:v>
       </x:c>
       <x:c r="I58" s="704" t="str">
         <x:v>SCR-002</x:v>
@@ -6427,7 +6427,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="69" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="69" t="str">
         <x:v>Ver.2.4</x:v>
@@ -6676,15 +6676,31 @@
       <x:c r="K13" s="111"/>
       <x:c r="L13" s="111"/>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14"/>
-      <x:c r="B14"/>
-      <x:c r="C14"/>
-      <x:c r="D14"/>
-      <x:c r="E14"/>
-      <x:c r="F14"/>
-      <x:c r="G14"/>
-      <x:c r="H14"/>
+    <x:row r="14" ht="95" customHeight="1">
+      <x:c r="A14" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>2026-09-29</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>改訂</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>U-01対応：menus固定Codeの契約参照・正常応答Mockを同期。Login業務処理は変更なし。</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>未記入</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>未確認</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
       <x:c r="I14" s="2"/>
       <x:c r="J14" s="2"/>
       <x:c r="K14" s="2"/>
@@ -6906,7 +6922,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
         <x:v>Ver.2.4</x:v>
@@ -8513,7 +8529,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
         <x:v>Ver.2.4</x:v>
@@ -10173,7 +10189,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
         <x:v>Ver.2.4</x:v>
@@ -11829,7 +11845,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
         <x:v>Ver.2.4</x:v>
@@ -13451,7 +13467,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
         <x:v>Ver.2.4</x:v>
@@ -15983,7 +15999,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
         <x:v>Ver.2.4</x:v>
@@ -16840,7 +16856,7 @@
       <x:c r="K41" s="111"/>
       <x:c r="L41" s="111"/>
     </x:row>
-    <x:row r="42" ht="48" hidden="0" customHeight="1">
+    <x:row r="42" ht="90" hidden="0" customHeight="1">
       <x:c r="A42" s="529" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -16860,10 +16876,10 @@
         <x:v>変換しない</x:v>
       </x:c>
       <x:c r="G42" s="529" t="str">
-        <x:v>空配列可</x:v>
+        <x:v>空配列可。配列・要素Null不可</x:v>
       </x:c>
       <x:c r="H42" s="529" t="str">
-        <x:v>共通Menu表示</x:v>
+        <x:v>02の固定Menu Code。表示Binding・重複/未知Code防御はCMN-FE-001 CFG-05/S022</x:v>
       </x:c>
       <x:c r="I42" s="529" t="str">
         <x:v>EVT-001 Step5／EVT-002 Step8</x:v>
@@ -18197,7 +18213,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
         <x:v>Ver.2.4</x:v>

--- a/詳細設計/画面詳細設計/01_SCR-001_ログイン画面詳細設計書_React.xlsx
+++ b/詳細設計/画面詳細設計/01_SCR-001_ログイン画面詳細設計書_React.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <ns0:sheets>
-    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="Rc7806f27c0ea4791"/>
-    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="R29264a1decdd4084"/>
-    <ns0:sheet name="02_画面概要" sheetId="3" ns1:id="R4f86f793e7ce4353"/>
-    <ns0:sheet name="03_画面レイアウト" sheetId="4" ns1:id="R1b401617af2942de"/>
-    <ns0:sheet name="04_画面項目" sheetId="5" ns1:id="Rc28523823f7f451f"/>
-    <ns0:sheet name="05_Component_State" sheetId="6" ns1:id="R32a08b7872be4749"/>
-    <ns0:sheet name="06_Event処理" sheetId="7" ns1:id="R12c58aef70d74c94"/>
-    <ns0:sheet name="07_API_Mapping" sheetId="8" ns1:id="Rb47a07ec5eb145b1"/>
-    <ns0:sheet name="08_Message_例外" sheetId="9" ns1:id="R3d856f5d82e04a7d"/>
-    <ns0:sheet name="09_単体テスト観点" sheetId="10" ns1:id="R485988af67d74eb1"/>
-  </ns0:sheets>
-</ns0:workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Ra1b7ee0331e64488"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R1b90a3466e6640fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_画面概要" sheetId="3" r:id="R14df56d2f6544766"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_画面レイアウト" sheetId="4" r:id="Rcf2b15a0292e4f90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_画面項目" sheetId="5" r:id="R5e0bfe9d9e814629"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Component_State" sheetId="6" r:id="R8964578264454543"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Event処理" sheetId="7" r:id="Re88775cb1d994454"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_API_Mapping" sheetId="8" r:id="Rbebffd10eddd47f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Message_例外" sheetId="9" r:id="R583a1c3c555c44a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_単体テスト観点" sheetId="10" r:id="R04d8ee08fc7a4830"/>
+  </x:sheets>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22,6 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
   <x:fonts count="28">
     <x:font>
       <x:sz val="11"/>
@@ -877,7 +880,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="706">
+  <x:cellXfs count="708">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2928,6 +2931,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="20" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -3492,119 +3499,50 @@
       <x:c r="K21" s="2"/>
       <x:c r="L21" s="2"/>
     </x:row>
-    <x:row r="22" ht="44" customHeight="1">
+    <x:row r="22" ht="72" customHeight="1">
       <x:c r="A22" s="58" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01＋CHG-MENU-20260929-01（02 Ver.2.6・10 Ver.2.7）。menus契約・Mockを同期。既存Login処理・権限は変更なし。正式承認は別途記録。</x:v>
-      </x:c>
-      <x:c r="B22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="C22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="D22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="E22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="F22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="G22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="H22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="I22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="J22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="K22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="L22" s="60" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
+        <x:v>文書状態：Review済／承認待ち。二次Review日：2026-09-30。
+参照：BL-2026-09-24＋CHG-AUTH-20260928-01＋CHG-MENU-20260929-01（02 Ver.2.6・10 Ver.2.7）。menus契約・Mockを同期。既存Login処理・権限は変更なし。正式承認は別途記録。</x:v>
+      </x:c>
+      <x:c r="B22" s="59"/>
+      <x:c r="C22" s="59"/>
+      <x:c r="D22" s="59"/>
+      <x:c r="E22" s="59"/>
+      <x:c r="F22" s="59"/>
+      <x:c r="G22" s="59"/>
+      <x:c r="H22" s="59"/>
+      <x:c r="I22" s="59"/>
+      <x:c r="J22" s="59"/>
+      <x:c r="K22" s="59"/>
+      <x:c r="L22" s="60"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="61" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="B23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="C23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="D23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="E23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="F23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="G23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="H23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="I23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="J23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="K23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="L23" s="63" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
+      <x:c r="A23" s="61"/>
+      <x:c r="B23" s="62"/>
+      <x:c r="C23" s="62"/>
+      <x:c r="D23" s="62"/>
+      <x:c r="E23" s="62"/>
+      <x:c r="F23" s="62"/>
+      <x:c r="G23" s="62"/>
+      <x:c r="H23" s="62"/>
+      <x:c r="I23" s="62"/>
+      <x:c r="J23" s="62"/>
+      <x:c r="K23" s="62"/>
+      <x:c r="L23" s="63"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="64" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="B24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="C24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="D24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="E24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="F24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="G24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="H24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="I24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="J24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="K24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="L24" s="66" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
+      <x:c r="A24" s="64"/>
+      <x:c r="B24" s="65"/>
+      <x:c r="C24" s="65"/>
+      <x:c r="D24" s="65"/>
+      <x:c r="E24" s="65"/>
+      <x:c r="F24" s="65"/>
+      <x:c r="G24" s="65"/>
+      <x:c r="H24" s="65"/>
+      <x:c r="I24" s="65"/>
+      <x:c r="J24" s="65"/>
+      <x:c r="K24" s="65"/>
+      <x:c r="L24" s="66"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="2"/>
@@ -6706,15 +6644,31 @@
       <x:c r="K14" s="2"/>
       <x:c r="L14" s="2"/>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15"/>
-      <x:c r="B15"/>
-      <x:c r="C15"/>
-      <x:c r="D15"/>
-      <x:c r="E15"/>
-      <x:c r="F15"/>
-      <x:c r="G15"/>
-      <x:c r="H15"/>
+    <x:row r="15" ht="84" customHeight="1">
+      <x:c r="A15" s="486" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B15" s="707" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="C15" s="486" t="str">
+        <x:v>Review</x:v>
+      </x:c>
+      <x:c r="D15" s="486" t="str">
+        <x:v>二次Review完了。AUTH-004参照を基本設計正本へ整理。Flow・UT変更なし。</x:v>
+      </x:c>
+      <x:c r="E15" s="486" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F15" s="486" t="str">
+        <x:v>Review済</x:v>
+      </x:c>
+      <x:c r="G15" s="486" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H15" s="486" t="str">
+        <x:v>承認待ち</x:v>
+      </x:c>
       <x:c r="I15" s="2"/>
       <x:c r="J15" s="2"/>
       <x:c r="K15" s="2"/>
@@ -16212,7 +16166,7 @@
         <x:v>CMN-FE-002</x:v>
       </x:c>
       <x:c r="K11" s="81" t="str">
-        <x:v>004_API-AUTH-004_現在ユーザー・権限取得API詳細設計書</x:v>
+        <x:v>10_API共通と認証_基本設計書／23_API項目定義（API-AUTH-004）。API-AUTH-004詳細設計は後続作成対象。</x:v>
       </x:c>
       <x:c r="L11" s="111"/>
     </x:row>

--- a/詳細設計/画面詳細設計/01_SCR-001_ログイン画面詳細設計書_React.xlsx
+++ b/詳細設計/画面詳細設計/01_SCR-001_ログイン画面詳細設計書_React.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Ra1b7ee0331e64488"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R1b90a3466e6640fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_画面概要" sheetId="3" r:id="R14df56d2f6544766"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_画面レイアウト" sheetId="4" r:id="Rcf2b15a0292e4f90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_画面項目" sheetId="5" r:id="R5e0bfe9d9e814629"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Component_State" sheetId="6" r:id="R8964578264454543"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Event処理" sheetId="7" r:id="Re88775cb1d994454"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_API_Mapping" sheetId="8" r:id="Rbebffd10eddd47f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Message_例外" sheetId="9" r:id="R583a1c3c555c44a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_単体テスト観点" sheetId="10" r:id="R04d8ee08fc7a4830"/>
-  </x:sheets>
-</x:workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheets>
+    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="Rc7806f27c0ea4791"/>
+    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="R29264a1decdd4084"/>
+    <ns0:sheet name="02_画面概要" sheetId="3" ns1:id="R4f86f793e7ce4353"/>
+    <ns0:sheet name="03_画面レイアウト" sheetId="4" ns1:id="R1b401617af2942de"/>
+    <ns0:sheet name="04_画面項目" sheetId="5" ns1:id="Rc28523823f7f451f"/>
+    <ns0:sheet name="05_Component_State" sheetId="6" ns1:id="R32a08b7872be4749"/>
+    <ns0:sheet name="06_Event処理" sheetId="7" ns1:id="R12c58aef70d74c94"/>
+    <ns0:sheet name="07_API_Mapping" sheetId="8" ns1:id="Rb47a07ec5eb145b1"/>
+    <ns0:sheet name="08_Message_例外" sheetId="9" ns1:id="R3d856f5d82e04a7d"/>
+    <ns0:sheet name="09_単体テスト観点" sheetId="10" ns1:id="R485988af67d74eb1"/>
+  </ns0:sheets>
+</ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22,9 +22,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
-  </x:numFmts>
   <x:fonts count="28">
     <x:font>
       <x:sz val="11"/>
@@ -880,7 +877,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="708">
+  <x:cellXfs count="706">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2931,10 +2928,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="20" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -3499,50 +3492,119 @@
       <x:c r="K21" s="2"/>
       <x:c r="L21" s="2"/>
     </x:row>
-    <x:row r="22" ht="72" customHeight="1">
+    <x:row r="22" ht="44" customHeight="1">
       <x:c r="A22" s="58" t="str">
-        <x:v>文書状態：Review済／承認待ち。二次Review日：2026-09-30。
-参照：BL-2026-09-24＋CHG-AUTH-20260928-01＋CHG-MENU-20260929-01（02 Ver.2.6・10 Ver.2.7）。menus契約・Mockを同期。既存Login処理・権限は変更なし。正式承認は別途記録。</x:v>
-      </x:c>
-      <x:c r="B22" s="59"/>
-      <x:c r="C22" s="59"/>
-      <x:c r="D22" s="59"/>
-      <x:c r="E22" s="59"/>
-      <x:c r="F22" s="59"/>
-      <x:c r="G22" s="59"/>
-      <x:c r="H22" s="59"/>
-      <x:c r="I22" s="59"/>
-      <x:c r="J22" s="59"/>
-      <x:c r="K22" s="59"/>
-      <x:c r="L22" s="60"/>
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01＋CHG-MENU-20260929-01（02 Ver.2.6・10 Ver.2.7）。menus契約・Mockを同期。既存Login処理・権限は変更なし。正式承認は別途記録。</x:v>
+      </x:c>
+      <x:c r="B22" s="59" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="C22" s="59" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="D22" s="59" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="E22" s="59" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="F22" s="59" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="G22" s="59" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="H22" s="59" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="I22" s="59" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="J22" s="59" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="K22" s="59" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="L22" s="60" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="61"/>
-      <x:c r="B23" s="62"/>
-      <x:c r="C23" s="62"/>
-      <x:c r="D23" s="62"/>
-      <x:c r="E23" s="62"/>
-      <x:c r="F23" s="62"/>
-      <x:c r="G23" s="62"/>
-      <x:c r="H23" s="62"/>
-      <x:c r="I23" s="62"/>
-      <x:c r="J23" s="62"/>
-      <x:c r="K23" s="62"/>
-      <x:c r="L23" s="63"/>
+      <x:c r="A23" s="61" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="B23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="C23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="D23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="E23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="F23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="G23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="H23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="I23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="J23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="K23" s="62" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="L23" s="63" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="64"/>
-      <x:c r="B24" s="65"/>
-      <x:c r="C24" s="65"/>
-      <x:c r="D24" s="65"/>
-      <x:c r="E24" s="65"/>
-      <x:c r="F24" s="65"/>
-      <x:c r="G24" s="65"/>
-      <x:c r="H24" s="65"/>
-      <x:c r="I24" s="65"/>
-      <x:c r="J24" s="65"/>
-      <x:c r="K24" s="65"/>
-      <x:c r="L24" s="66"/>
+      <x:c r="A24" s="64" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="B24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="C24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="D24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="E24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="F24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="G24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="H24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="I24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="J24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="K24" s="65" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
+      <x:c r="L24" s="66" t="str">
+        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="2"/>
@@ -6644,31 +6706,15 @@
       <x:c r="K14" s="2"/>
       <x:c r="L14" s="2"/>
     </x:row>
-    <x:row r="15" ht="84" customHeight="1">
-      <x:c r="A15" s="486" t="str">
-        <x:v>Ver.2.5</x:v>
-      </x:c>
-      <x:c r="B15" s="707" t="n">
-        <x:v>46295</x:v>
-      </x:c>
-      <x:c r="C15" s="486" t="str">
-        <x:v>Review</x:v>
-      </x:c>
-      <x:c r="D15" s="486" t="str">
-        <x:v>二次Review完了。AUTH-004参照を基本設計正本へ整理。Flow・UT変更なし。</x:v>
-      </x:c>
-      <x:c r="E15" s="486" t="str">
-        <x:v>－</x:v>
-      </x:c>
-      <x:c r="F15" s="486" t="str">
-        <x:v>Review済</x:v>
-      </x:c>
-      <x:c r="G15" s="486" t="str">
-        <x:v>－</x:v>
-      </x:c>
-      <x:c r="H15" s="486" t="str">
-        <x:v>承認待ち</x:v>
-      </x:c>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
       <x:c r="I15" s="2"/>
       <x:c r="J15" s="2"/>
       <x:c r="K15" s="2"/>
@@ -16166,7 +16212,7 @@
         <x:v>CMN-FE-002</x:v>
       </x:c>
       <x:c r="K11" s="81" t="str">
-        <x:v>10_API共通と認証_基本設計書／23_API項目定義（API-AUTH-004）。API-AUTH-004詳細設計は後続作成対象。</x:v>
+        <x:v>004_API-AUTH-004_現在ユーザー・権限取得API詳細設計書</x:v>
       </x:c>
       <x:c r="L11" s="111"/>
     </x:row>

--- a/詳細設計/画面詳細設計/01_SCR-001_ログイン画面詳細設計書_React.xlsx
+++ b/詳細設計/画面詳細設計/01_SCR-001_ログイン画面詳細設計書_React.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rb3ff751f98324b88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Ra713412ff8264d5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_画面概要" sheetId="3" r:id="R5ae780e457f4443e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_画面レイアウト" sheetId="4" r:id="R171af198e2154e3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_画面項目" sheetId="5" r:id="R37cd7aaf898545ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Component_State" sheetId="6" r:id="R354d20bef5d649b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Event処理" sheetId="7" r:id="Rd2374e67b1e54c0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_API_Mapping" sheetId="8" r:id="R2f36e49c669344f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Message_例外" sheetId="9" r:id="R486eb63b9c1747a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_単体テスト観点" sheetId="10" r:id="R18ef82a3d2114434"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Ra1b7ee0331e64488"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R1b90a3466e6640fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_画面概要" sheetId="3" r:id="R14df56d2f6544766"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_画面レイアウト" sheetId="4" r:id="Rcf2b15a0292e4f90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_画面項目" sheetId="5" r:id="R5e0bfe9d9e814629"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Component_State" sheetId="6" r:id="R8964578264454543"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Event処理" sheetId="7" r:id="Re88775cb1d994454"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_API_Mapping" sheetId="8" r:id="Rbebffd10eddd47f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Message_例外" sheetId="9" r:id="R583a1c3c555c44a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_単体テスト観点" sheetId="10" r:id="R04d8ee08fc7a4830"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,6 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
   <x:fonts count="28">
     <x:font>
       <x:sz val="11"/>
@@ -877,7 +880,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="706">
+  <x:cellXfs count="708">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2928,6 +2931,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="20" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -3189,7 +3196,7 @@
       <x:c r="H2" s="2"/>
       <x:c r="I2" s="2"/>
       <x:c r="J2" s="2" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="2"/>
       <x:c r="L2" s="2"/>
@@ -3379,7 +3386,7 @@
       <x:c r="D15" s="36"/>
       <x:c r="E15" s="36"/>
       <x:c r="F15" s="38" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="G15" s="38" t="str">
         <x:v>Ver.2.4</x:v>
@@ -3492,119 +3499,50 @@
       <x:c r="K21" s="2"/>
       <x:c r="L21" s="2"/>
     </x:row>
-    <x:row r="22" ht="44" customHeight="1">
+    <x:row r="22" ht="72" customHeight="1">
       <x:c r="A22" s="58" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="B22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="C22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="D22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="E22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="F22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="G22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="H22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="I22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="J22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="K22" s="59" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="L22" s="60" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
+        <x:v>文書状態：Review済／承認待ち。二次Review日：2026-09-30。
+参照：BL-2026-09-24＋CHG-AUTH-20260928-01＋CHG-MENU-20260929-01（02 Ver.2.6・10 Ver.2.7）。menus契約・Mockを同期。既存Login処理・権限は変更なし。正式承認は別途記録。</x:v>
+      </x:c>
+      <x:c r="B22" s="59"/>
+      <x:c r="C22" s="59"/>
+      <x:c r="D22" s="59"/>
+      <x:c r="E22" s="59"/>
+      <x:c r="F22" s="59"/>
+      <x:c r="G22" s="59"/>
+      <x:c r="H22" s="59"/>
+      <x:c r="I22" s="59"/>
+      <x:c r="J22" s="59"/>
+      <x:c r="K22" s="59"/>
+      <x:c r="L22" s="60"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="61" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="B23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="C23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="D23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="E23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="F23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="G23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="H23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="I23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="J23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="K23" s="62" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="L23" s="63" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
+      <x:c r="A23" s="61"/>
+      <x:c r="B23" s="62"/>
+      <x:c r="C23" s="62"/>
+      <x:c r="D23" s="62"/>
+      <x:c r="E23" s="62"/>
+      <x:c r="F23" s="62"/>
+      <x:c r="G23" s="62"/>
+      <x:c r="H23" s="62"/>
+      <x:c r="I23" s="62"/>
+      <x:c r="J23" s="62"/>
+      <x:c r="K23" s="62"/>
+      <x:c r="L23" s="63"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="64" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="B24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="C24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="D24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="E24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="F24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="G24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="H24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="I24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="J24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="K24" s="65" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
-      <x:c r="L24" s="66" t="str">
-        <x:v>参照：BL-2026-09-24＋CHG-AUTH-20260928-01（10・16・19 Ver.2.6、変更反映済／承認待ち）。SCR-001固有処理を展開する。Review修正済、正式承認はProject Leaderが記録する。</x:v>
-      </x:c>
+      <x:c r="A24" s="64"/>
+      <x:c r="B24" s="65"/>
+      <x:c r="C24" s="65"/>
+      <x:c r="D24" s="65"/>
+      <x:c r="E24" s="65"/>
+      <x:c r="F24" s="65"/>
+      <x:c r="G24" s="65"/>
+      <x:c r="H24" s="65"/>
+      <x:c r="I24" s="65"/>
+      <x:c r="J24" s="65"/>
+      <x:c r="K24" s="65"/>
+      <x:c r="L24" s="66"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="2"/>
@@ -3763,7 +3701,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
         <x:v>Ver.2.4</x:v>
@@ -5520,7 +5458,7 @@
         <x:v>07行54；08 No.10</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="160" customHeight="1">
+    <x:row r="58" ht="285" customHeight="1">
       <x:c r="A58" s="704" t="str">
         <x:v>UT-033</x:v>
       </x:c>
@@ -5537,13 +5475,13 @@
         <x:v>/loginを表示</x:v>
       </x:c>
       <x:c r="F58" s="704" t="str">
-        <x:v>200：user.id=1、employeeId=1001（数値）、name=社員A、roles=[EMP]、permissions=[]、menus=[]、passwordMustChange=false。共通Envelopeは契約どおり</x:v>
+        <x:v>200：user.id=1、employeeId=1001（数値）、name=社員A、roles=[ROLE-EMP]、permissions=["PERM-DASH-READ","PERM-PRJ-READ","PERM-TASK-READ","PERM-TASK-PROGRESS","PERM-RPT-SELF","PERM-FILE-WRITE"]、menus=["MENU-HOME","MENU-PROJECTS","MENU-MY-PROJECTS","MENU-MY-TASKS","MENU-TASK-BOARD","MENU-MY-REPORTS","MENU-NOTIFICATIONS"]、passwordMustChange=false。Envelopeは契約どおり。</x:v>
       </x:c>
       <x:c r="G58" s="704" t="str">
         <x:v>Schema Errorなし</x:v>
       </x:c>
       <x:c r="H58" s="704" t="str">
-        <x:v>employeeIdは数値、menusはstring[]として保存。余分な変換なし</x:v>
+        <x:v>employeeIdは数値。menusは受信した固定Code配列としてSTATE-008へ保存し、表示名へ変換しない。共通01 S022へ渡す。</x:v>
       </x:c>
       <x:c r="I58" s="704" t="str">
         <x:v>SCR-002</x:v>
@@ -6427,7 +6365,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="69" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="69" t="str">
         <x:v>Ver.2.4</x:v>
@@ -6676,29 +6614,61 @@
       <x:c r="K13" s="111"/>
       <x:c r="L13" s="111"/>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14"/>
-      <x:c r="B14"/>
-      <x:c r="C14"/>
-      <x:c r="D14"/>
-      <x:c r="E14"/>
-      <x:c r="F14"/>
-      <x:c r="G14"/>
-      <x:c r="H14"/>
+    <x:row r="14" ht="95" customHeight="1">
+      <x:c r="A14" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>2026-09-29</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>改訂</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>U-01対応：menus固定Codeの契約参照・正常応答Mockを同期。Login業務処理は変更なし。</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>未記入</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>未確認</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
       <x:c r="I14" s="2"/>
       <x:c r="J14" s="2"/>
       <x:c r="K14" s="2"/>
       <x:c r="L14" s="2"/>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15"/>
-      <x:c r="B15"/>
-      <x:c r="C15"/>
-      <x:c r="D15"/>
-      <x:c r="E15"/>
-      <x:c r="F15"/>
-      <x:c r="G15"/>
-      <x:c r="H15"/>
+    <x:row r="15" ht="84" customHeight="1">
+      <x:c r="A15" s="486" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B15" s="707" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="C15" s="486" t="str">
+        <x:v>Review</x:v>
+      </x:c>
+      <x:c r="D15" s="486" t="str">
+        <x:v>二次Review完了。AUTH-004参照を基本設計正本へ整理。Flow・UT変更なし。</x:v>
+      </x:c>
+      <x:c r="E15" s="486" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F15" s="486" t="str">
+        <x:v>Review済</x:v>
+      </x:c>
+      <x:c r="G15" s="486" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H15" s="486" t="str">
+        <x:v>承認待ち</x:v>
+      </x:c>
       <x:c r="I15" s="2"/>
       <x:c r="J15" s="2"/>
       <x:c r="K15" s="2"/>
@@ -6906,7 +6876,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
         <x:v>Ver.2.4</x:v>
@@ -8513,7 +8483,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
         <x:v>Ver.2.4</x:v>
@@ -10173,7 +10143,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
         <x:v>Ver.2.4</x:v>
@@ -11829,7 +11799,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
         <x:v>Ver.2.4</x:v>
@@ -13451,7 +13421,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
         <x:v>Ver.2.4</x:v>
@@ -15983,7 +15953,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
         <x:v>Ver.2.4</x:v>
@@ -16196,7 +16166,7 @@
         <x:v>CMN-FE-002</x:v>
       </x:c>
       <x:c r="K11" s="81" t="str">
-        <x:v>004_API-AUTH-004_現在ユーザー・権限取得API詳細設計書</x:v>
+        <x:v>10_API共通と認証_基本設計書／23_API項目定義（API-AUTH-004）。API-AUTH-004詳細設計は後続作成対象。</x:v>
       </x:c>
       <x:c r="L11" s="111"/>
     </x:row>
@@ -16840,7 +16810,7 @@
       <x:c r="K41" s="111"/>
       <x:c r="L41" s="111"/>
     </x:row>
-    <x:row r="42" ht="48" hidden="0" customHeight="1">
+    <x:row r="42" ht="90" hidden="0" customHeight="1">
       <x:c r="A42" s="529" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -16860,10 +16830,10 @@
         <x:v>変換しない</x:v>
       </x:c>
       <x:c r="G42" s="529" t="str">
-        <x:v>空配列可</x:v>
+        <x:v>空配列可。配列・要素Null不可</x:v>
       </x:c>
       <x:c r="H42" s="529" t="str">
-        <x:v>共通Menu表示</x:v>
+        <x:v>02の固定Menu Code。表示Binding・重複/未知Code防御はCMN-FE-001 CFG-05/S022</x:v>
       </x:c>
       <x:c r="I42" s="529" t="str">
         <x:v>EVT-001 Step5／EVT-002 Step8</x:v>
@@ -18197,7 +18167,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
         <x:v>Ver.2.4</x:v>
